--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104489</v>
+        <v>104492</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104492</v>
+        <v>104493</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136189491</v>
       </c>
       <c r="B11" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136189460</v>
       </c>
       <c r="B13" t="n">
-        <v>80013</v>
+        <v>80015</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136189487</v>
       </c>
       <c r="B19" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136189489</v>
       </c>
       <c r="B20" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189451</v>
       </c>
       <c r="B21" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104493</v>
+        <v>104498</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104498</v>
+        <v>104500</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
